--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260911.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260911.xlsx
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>39,353,000</t>
+          <t>12,488,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>12,488,000</t>
+          <t>39,353,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>28,492,899</t>
+          <t>14,300,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>14,300,000</t>
+          <t>28,492,899</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
